--- a/AE-marketingrapport-master.xlsx
+++ b/AE-marketingrapport-master.xlsx
@@ -13760,40 +13760,43 @@
         <v>123372</v>
       </c>
       <c r="O134" s="117" t="n">
-        <v>90423</v>
+        <v>111033</v>
       </c>
       <c r="P134" s="117" t="n">
-        <v>236178</v>
+        <v>255948</v>
       </c>
       <c r="Q134" s="117" t="n">
-        <v>483833</v>
+        <v>505463</v>
       </c>
       <c r="R134" s="117" t="n">
-        <v>260490</v>
+        <v>292920</v>
       </c>
       <c r="S134" s="117" t="n">
-        <v>142208</v>
+        <v>168218</v>
       </c>
       <c r="T134" s="117" t="n">
-        <v>168218</v>
+        <v>233205</v>
       </c>
       <c r="U134" s="117" t="n">
-        <v>233205</v>
+        <v>241899</v>
       </c>
       <c r="V134" s="117" t="n">
-        <v>241899</v>
+        <v>355220</v>
       </c>
       <c r="W134" s="117" t="n">
-        <v>355220</v>
+        <v>323030</v>
       </c>
       <c r="X134" s="117" t="n">
-        <v>236530</v>
+        <v>313735</v>
       </c>
       <c r="Y134" s="117" t="n">
-        <v>296715</v>
+        <v>296714.7</v>
       </c>
       <c r="Z134" s="117" t="n">
-        <v>394660</v>
+        <v>394659.99</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>315652.77</v>
       </c>
     </row>
   </sheetData>

--- a/AE-marketingrapport-master.xlsx
+++ b/AE-marketingrapport-master.xlsx
@@ -4284,7 +4284,9 @@
       <c r="AA5" s="149" t="n">
         <v>16284</v>
       </c>
-      <c r="AB5" s="149" t="n"/>
+      <c r="AB5" s="149" t="n">
+        <v>27344</v>
+      </c>
       <c r="AC5" s="149" t="n"/>
       <c r="AD5" s="149" t="n"/>
       <c r="AE5" s="149" t="n"/>
@@ -4370,7 +4372,9 @@
       <c r="AA6" s="149" t="n">
         <v>188552</v>
       </c>
-      <c r="AB6" s="149" t="n"/>
+      <c r="AB6" s="149" t="n">
+        <v>223517</v>
+      </c>
       <c r="AC6" s="149" t="n"/>
       <c r="AD6" s="149" t="n"/>
       <c r="AE6" s="149" t="n"/>
@@ -4456,7 +4460,9 @@
       <c r="AA7" s="149" t="n">
         <v>2860</v>
       </c>
-      <c r="AB7" s="149" t="n"/>
+      <c r="AB7" s="149" t="n">
+        <v>3810</v>
+      </c>
       <c r="AC7" s="149" t="n"/>
       <c r="AD7" s="149" t="n"/>
       <c r="AE7" s="149" t="n"/>
@@ -4542,7 +4548,9 @@
       <c r="AA8" s="149" t="n">
         <v>72</v>
       </c>
-      <c r="AB8" s="149" t="n"/>
+      <c r="AB8" s="149" t="n">
+        <v>97</v>
+      </c>
       <c r="AC8" s="149" t="n"/>
       <c r="AD8" s="149" t="n"/>
       <c r="AE8" s="149" t="n"/>
@@ -4875,7 +4883,9 @@
       <c r="AA12" s="149" t="n">
         <v>7371</v>
       </c>
-      <c r="AB12" s="149" t="n"/>
+      <c r="AB12" s="149" t="n">
+        <v>10442.98</v>
+      </c>
       <c r="AC12" s="149" t="n"/>
       <c r="AD12" s="149" t="n"/>
       <c r="AE12" s="149" t="n"/>
@@ -4941,7 +4951,9 @@
       <c r="AA13" s="149" t="n">
         <v>15817</v>
       </c>
-      <c r="AB13" s="149" t="n"/>
+      <c r="AB13" s="149" t="n">
+        <v>24955</v>
+      </c>
       <c r="AC13" s="149" t="n"/>
       <c r="AD13" s="149" t="n"/>
       <c r="AE13" s="149" t="n"/>
@@ -5007,7 +5019,9 @@
       <c r="AA14" s="149" t="n">
         <v>801</v>
       </c>
-      <c r="AB14" s="149" t="n"/>
+      <c r="AB14" s="149" t="n">
+        <v>1320</v>
+      </c>
       <c r="AC14" s="149" t="n"/>
       <c r="AD14" s="149" t="n"/>
       <c r="AE14" s="149" t="n"/>
@@ -5073,7 +5087,9 @@
       <c r="AA15" s="149" t="n">
         <v>81</v>
       </c>
-      <c r="AB15" s="149" t="n"/>
+      <c r="AB15" s="149" t="n">
+        <v>82</v>
+      </c>
       <c r="AC15" s="149" t="n"/>
       <c r="AD15" s="149" t="n"/>
       <c r="AE15" s="149" t="n"/>
@@ -5386,7 +5402,9 @@
       <c r="AA19" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" s="149" t="n"/>
+      <c r="AB19" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC19" s="149" t="n"/>
       <c r="AD19" s="149" t="n"/>
       <c r="AE19" s="149" t="n"/>
@@ -5432,7 +5450,9 @@
       <c r="AA20" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB20" s="149" t="n"/>
+      <c r="AB20" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC20" s="149" t="n"/>
       <c r="AD20" s="149" t="n"/>
       <c r="AE20" s="149" t="n"/>
@@ -5478,7 +5498,9 @@
       <c r="AA21" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" s="149" t="n"/>
+      <c r="AB21" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC21" s="149" t="n"/>
       <c r="AD21" s="149" t="n"/>
       <c r="AE21" s="149" t="n"/>
@@ -5524,7 +5546,9 @@
       <c r="AA22" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB22" s="149" t="n"/>
+      <c r="AB22" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC22" s="149" t="n"/>
       <c r="AD22" s="149" t="n"/>
       <c r="AE22" s="149" t="n"/>
@@ -5835,7 +5859,9 @@
       <c r="AA26" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB26" s="149" t="n"/>
+      <c r="AB26" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC26" s="149" t="n"/>
       <c r="AD26" s="149" t="n"/>
       <c r="AE26" s="149" t="n"/>
@@ -5879,7 +5905,9 @@
       <c r="AA27" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB27" s="149" t="n"/>
+      <c r="AB27" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC27" s="149" t="n"/>
       <c r="AD27" s="149" t="n"/>
       <c r="AE27" s="149" t="n"/>
@@ -5923,7 +5951,9 @@
       <c r="AA28" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB28" s="149" t="n"/>
+      <c r="AB28" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC28" s="149" t="n"/>
       <c r="AD28" s="149" t="n"/>
       <c r="AE28" s="149" t="n"/>
@@ -5967,7 +5997,9 @@
       <c r="AA29" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB29" s="149" t="n"/>
+      <c r="AB29" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC29" s="149" t="n"/>
       <c r="AD29" s="149" t="n"/>
       <c r="AE29" s="149" t="n"/>
@@ -6320,7 +6352,9 @@
       <c r="AA33" s="149" t="n">
         <v>2832</v>
       </c>
-      <c r="AB33" s="149" t="n"/>
+      <c r="AB33" s="149" t="n">
+        <v>2896.4</v>
+      </c>
       <c r="AC33" s="149" t="n"/>
       <c r="AD33" s="149" t="n"/>
       <c r="AE33" s="149" t="n"/>
@@ -6402,7 +6436,9 @@
       <c r="AA34" s="149" t="n">
         <v>10292</v>
       </c>
-      <c r="AB34" s="149" t="n"/>
+      <c r="AB34" s="149" t="n">
+        <v>10740</v>
+      </c>
       <c r="AC34" s="149" t="n"/>
       <c r="AD34" s="149" t="n"/>
       <c r="AE34" s="149" t="n"/>
@@ -6488,7 +6524,9 @@
       <c r="AA35" s="149" t="n">
         <v>5042</v>
       </c>
-      <c r="AB35" s="149" t="n"/>
+      <c r="AB35" s="149" t="n">
+        <v>5474</v>
+      </c>
       <c r="AC35" s="149" t="n"/>
       <c r="AD35" s="149" t="n"/>
       <c r="AE35" s="149" t="n"/>
@@ -6574,7 +6612,9 @@
       <c r="AA36" s="149" t="n">
         <v>586</v>
       </c>
-      <c r="AB36" s="149" t="n"/>
+      <c r="AB36" s="149" t="n">
+        <v>481</v>
+      </c>
       <c r="AC36" s="149" t="n"/>
       <c r="AD36" s="149" t="n"/>
       <c r="AE36" s="149" t="n"/>
@@ -6894,7 +6934,9 @@
       <c r="AA41" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB41" s="149" t="n"/>
+      <c r="AB41" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC41" s="149" t="n"/>
       <c r="AD41" s="149" t="n"/>
       <c r="AE41" s="149" t="n"/>
@@ -6940,7 +6982,9 @@
       <c r="AA42" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB42" s="149" t="n"/>
+      <c r="AB42" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC42" s="149" t="n"/>
       <c r="AD42" s="149" t="n"/>
       <c r="AE42" s="149" t="n"/>
@@ -6984,7 +7028,9 @@
       <c r="AA43" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB43" s="149" t="n"/>
+      <c r="AB43" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC43" s="149" t="n"/>
       <c r="AD43" s="149" t="n"/>
       <c r="AE43" s="149" t="n"/>
@@ -7028,7 +7074,9 @@
       <c r="AA44" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB44" s="149" t="n"/>
+      <c r="AB44" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC44" s="149" t="n"/>
       <c r="AD44" s="149" t="n"/>
       <c r="AE44" s="149" t="n"/>
@@ -7363,7 +7411,9 @@
       <c r="AA48" s="149" t="n">
         <v>144500</v>
       </c>
-      <c r="AB48" s="149" t="n"/>
+      <c r="AB48" s="149" t="n">
+        <v>134500</v>
+      </c>
       <c r="AC48" s="149" t="n"/>
       <c r="AD48" s="149" t="n"/>
       <c r="AE48" s="149" t="n"/>
@@ -7413,7 +7463,9 @@
       <c r="AA49" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB49" s="149" t="n"/>
+      <c r="AB49" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC49" s="149" t="n"/>
       <c r="AD49" s="149" t="n"/>
       <c r="AE49" s="149" t="n"/>
@@ -7479,7 +7531,9 @@
       <c r="AA50" s="149" t="n">
         <v>3435</v>
       </c>
-      <c r="AB50" s="149" t="n"/>
+      <c r="AB50" s="149" t="n">
+        <v>5072</v>
+      </c>
       <c r="AC50" s="149" t="n"/>
       <c r="AD50" s="149" t="n"/>
       <c r="AE50" s="149" t="n"/>
@@ -7547,7 +7601,9 @@
       <c r="AA51" s="149" t="n">
         <v>289</v>
       </c>
-      <c r="AB51" s="149" t="n"/>
+      <c r="AB51" s="149" t="n">
+        <v>269</v>
+      </c>
       <c r="AC51" s="149" t="n"/>
       <c r="AD51" s="149" t="n"/>
       <c r="AE51" s="149" t="n"/>
@@ -7865,7 +7921,9 @@
       <c r="AA56" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB56" s="149" t="n"/>
+      <c r="AB56" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC56" s="149" t="n"/>
       <c r="AD56" s="149" t="n"/>
       <c r="AE56" s="149" t="n"/>
@@ -7909,7 +7967,9 @@
       <c r="AA57" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB57" s="149" t="n"/>
+      <c r="AB57" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC57" s="149" t="n"/>
       <c r="AD57" s="149" t="n"/>
       <c r="AE57" s="149" t="n"/>
@@ -7953,7 +8013,9 @@
       <c r="AA58" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB58" s="149" t="n"/>
+      <c r="AB58" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC58" s="149" t="n"/>
       <c r="AD58" s="149" t="n"/>
       <c r="AE58" s="149" t="n"/>
@@ -7997,7 +8059,9 @@
       <c r="AA59" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB59" s="149" t="n"/>
+      <c r="AB59" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC59" s="149" t="n"/>
       <c r="AD59" s="149" t="n"/>
       <c r="AE59" s="149" t="n"/>
@@ -8308,7 +8372,9 @@
       <c r="AA63" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB63" s="149" t="n"/>
+      <c r="AB63" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC63" s="149" t="n"/>
       <c r="AD63" s="149" t="n"/>
       <c r="AE63" s="149" t="n"/>
@@ -8352,7 +8418,9 @@
       <c r="AA64" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB64" s="149" t="n"/>
+      <c r="AB64" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC64" s="149" t="n"/>
       <c r="AD64" s="149" t="n"/>
       <c r="AE64" s="149" t="n"/>
@@ -8396,7 +8464,9 @@
       <c r="AA65" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB65" s="149" t="n"/>
+      <c r="AB65" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC65" s="149" t="n"/>
       <c r="AD65" s="149" t="n"/>
       <c r="AE65" s="149" t="n"/>
@@ -8440,7 +8510,9 @@
       <c r="AA66" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB66" s="149" t="n"/>
+      <c r="AB66" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC66" s="149" t="n"/>
       <c r="AD66" s="149" t="n"/>
       <c r="AE66" s="149" t="n"/>
@@ -8760,7 +8832,9 @@
       <c r="AA71" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB71" s="149" t="n"/>
+      <c r="AB71" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC71" s="149" t="n"/>
       <c r="AD71" s="149" t="n"/>
       <c r="AE71" s="149" t="n"/>
@@ -8806,7 +8880,9 @@
       <c r="AA72" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB72" s="149" t="n"/>
+      <c r="AB72" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC72" s="149" t="n"/>
       <c r="AD72" s="149" t="n"/>
       <c r="AE72" s="149" t="n"/>
@@ -8850,7 +8926,9 @@
       <c r="AA73" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB73" s="149" t="n"/>
+      <c r="AB73" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC73" s="149" t="n"/>
       <c r="AD73" s="149" t="n"/>
       <c r="AE73" s="149" t="n"/>
@@ -8896,7 +8974,9 @@
       <c r="AA74" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB74" s="149" t="n"/>
+      <c r="AB74" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC74" s="149" t="n"/>
       <c r="AD74" s="149" t="n"/>
       <c r="AE74" s="149" t="n"/>
@@ -9207,9 +9287,11 @@
         <v>3917.7</v>
       </c>
       <c r="AA78" s="149" t="n">
-        <v>4180</v>
-      </c>
-      <c r="AB78" s="149" t="n"/>
+        <v>4226.4</v>
+      </c>
+      <c r="AB78" s="149" t="n">
+        <v>4180.2</v>
+      </c>
       <c r="AC78" s="149" t="n"/>
       <c r="AD78" s="149" t="n"/>
       <c r="AE78" s="149" t="n"/>
@@ -9253,7 +9335,9 @@
       <c r="AA79" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB79" s="149" t="n"/>
+      <c r="AB79" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC79" s="149" t="n"/>
       <c r="AD79" s="149" t="n"/>
       <c r="AE79" s="149" t="n"/>
@@ -9297,7 +9381,9 @@
       <c r="AA80" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB80" s="149" t="n"/>
+      <c r="AB80" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC80" s="149" t="n"/>
       <c r="AD80" s="149" t="n"/>
       <c r="AE80" s="149" t="n"/>
@@ -9343,7 +9429,9 @@
       <c r="AA81" s="149" t="n">
         <v>16</v>
       </c>
-      <c r="AB81" s="149" t="n"/>
+      <c r="AB81" s="149" t="n">
+        <v>15</v>
+      </c>
       <c r="AC81" s="149" t="n"/>
       <c r="AD81" s="149" t="n"/>
       <c r="AE81" s="149" t="n"/>
@@ -9665,7 +9753,9 @@
       <c r="AA86" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB86" s="149" t="n"/>
+      <c r="AB86" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC86" s="149" t="n"/>
       <c r="AD86" s="149" t="n"/>
       <c r="AE86" s="149" t="n"/>
@@ -9711,7 +9801,9 @@
       <c r="AA87" s="149" t="n">
         <v>413000</v>
       </c>
-      <c r="AB87" s="149" t="n"/>
+      <c r="AB87" s="149" t="n">
+        <v>432000</v>
+      </c>
       <c r="AC87" s="149" t="n"/>
       <c r="AD87" s="149" t="n"/>
       <c r="AE87" s="149" t="n"/>
@@ -9783,7 +9875,9 @@
       <c r="AA88" s="149" t="n">
         <v>3700</v>
       </c>
-      <c r="AB88" s="149" t="n"/>
+      <c r="AB88" s="149" t="n">
+        <v>4470</v>
+      </c>
       <c r="AC88" s="149" t="n"/>
       <c r="AD88" s="149" t="n"/>
       <c r="AE88" s="149" t="n"/>
@@ -9839,7 +9933,9 @@
       <c r="AA89" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="AB89" s="149" t="n"/>
+      <c r="AB89" s="149" t="n">
+        <v>0</v>
+      </c>
       <c r="AC89" s="149" t="n"/>
       <c r="AD89" s="149" t="n"/>
       <c r="AE89" s="149" t="n"/>
@@ -10968,7 +11064,9 @@
       <c r="AA104" s="149" t="n">
         <v>189</v>
       </c>
-      <c r="AB104" s="149" t="n"/>
+      <c r="AB104" s="149" t="n">
+        <v>171</v>
+      </c>
       <c r="AC104" s="149" t="n"/>
       <c r="AD104" s="149" t="n"/>
       <c r="AE104" s="149" t="n"/>
@@ -11050,7 +11148,9 @@
       <c r="AA105" s="149" t="n">
         <v>16</v>
       </c>
-      <c r="AB105" s="149" t="n"/>
+      <c r="AB105" s="149" t="n">
+        <v>15</v>
+      </c>
       <c r="AC105" s="149" t="n"/>
       <c r="AD105" s="149" t="n"/>
       <c r="AE105" s="149" t="n"/>
@@ -11130,9 +11230,11 @@
         <v>3917.7</v>
       </c>
       <c r="AA106" s="149" t="n">
-        <v>4180</v>
-      </c>
-      <c r="AB106" s="149" t="n"/>
+        <v>4226.4</v>
+      </c>
+      <c r="AB106" s="149" t="n">
+        <v>4180.2</v>
+      </c>
       <c r="AC106" s="149" t="n"/>
       <c r="AD106" s="149" t="n"/>
       <c r="AE106" s="149" t="n"/>
@@ -13476,7 +13578,9 @@
       <c r="AA129" s="149" t="n">
         <v>1250</v>
       </c>
-      <c r="AB129" s="149" t="n"/>
+      <c r="AB129" s="149" t="n">
+        <v>1328</v>
+      </c>
       <c r="AC129" s="149" t="n"/>
       <c r="AD129" s="149" t="n"/>
       <c r="AE129" s="149" t="n"/>
@@ -13524,7 +13628,9 @@
       <c r="AA130" s="149" t="n">
         <v>8</v>
       </c>
-      <c r="AB130" s="149" t="n"/>
+      <c r="AB130" s="149" t="n">
+        <v>15</v>
+      </c>
       <c r="AC130" s="149" t="n"/>
       <c r="AD130" s="149" t="n"/>
       <c r="AE130" s="149" t="n"/>
@@ -13556,7 +13662,9 @@
       <c r="AA131" s="149" t="n">
         <v>618.33</v>
       </c>
-      <c r="AB131" s="149" t="n"/>
+      <c r="AB131" s="149" t="n">
+        <v>633.33</v>
+      </c>
       <c r="AC131" s="149" t="n"/>
       <c r="AD131" s="149" t="n"/>
       <c r="AE131" s="149" t="n"/>
@@ -13634,7 +13742,9 @@
       <c r="AA132" s="149" t="n">
         <v>14748</v>
       </c>
-      <c r="AB132" s="149" t="n"/>
+      <c r="AB132" s="149" t="n">
+        <v>15624</v>
+      </c>
       <c r="AC132" s="149" t="n"/>
       <c r="AD132" s="149" t="n"/>
       <c r="AE132" s="149" t="n"/>
@@ -13712,7 +13822,9 @@
       <c r="AA133" s="154" t="n">
         <v>0.025</v>
       </c>
-      <c r="AB133" s="154" t="n"/>
+      <c r="AB133" s="154" t="n">
+        <v>0.023</v>
+      </c>
       <c r="AC133" s="154" t="n"/>
       <c r="AD133" s="154" t="n"/>
       <c r="AE133" s="154" t="n"/>
@@ -13795,7 +13907,7 @@
       <c r="Z134" s="117" t="n">
         <v>394659.99</v>
       </c>
-      <c r="AA134" t="n">
+      <c r="AA134" s="117" t="n">
         <v>315652.77</v>
       </c>
     </row>
